--- a/artfynd/A 35927-2024 artfynd.xlsx
+++ b/artfynd/A 35927-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,210 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120459210</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Krögarkärret, Krögarkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>687170</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6667705</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120459848</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skällkovik, Skällkovik, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>686996</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6667475</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35927-2024 artfynd.xlsx
+++ b/artfynd/A 35927-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120459210</v>
+        <v>120459848</v>
       </c>
       <c r="B3" t="n">
         <v>91879</v>
@@ -826,14 +826,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krögarkärret, Krögarkärret, Upl</t>
+          <t>Skällkovik, Skällkovik, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687170</v>
+        <v>686996</v>
       </c>
       <c r="R3" t="n">
-        <v>6667705</v>
+        <v>6667475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120459848</v>
+        <v>120459210</v>
       </c>
       <c r="B4" t="n">
         <v>91879</v>
@@ -928,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skällkovik, Skällkovik, Upl</t>
+          <t>Krögarkärret, Krögarkärret, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686996</v>
+        <v>687170</v>
       </c>
       <c r="R4" t="n">
-        <v>6667475</v>
+        <v>6667705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 35927-2024 artfynd.xlsx
+++ b/artfynd/A 35927-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120459848</v>
+        <v>120459210</v>
       </c>
       <c r="B3" t="n">
         <v>91879</v>
@@ -826,14 +826,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skällkovik, Skällkovik, Upl</t>
+          <t>Krögarkärret, Krögarkärret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686996</v>
+        <v>687170</v>
       </c>
       <c r="R3" t="n">
-        <v>6667475</v>
+        <v>6667705</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120459210</v>
+        <v>120459848</v>
       </c>
       <c r="B4" t="n">
         <v>91879</v>
@@ -928,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krögarkärret, Krögarkärret, Upl</t>
+          <t>Skällkovik, Skällkovik, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687170</v>
+        <v>686996</v>
       </c>
       <c r="R4" t="n">
-        <v>6667705</v>
+        <v>6667475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
